--- a/survey_templates/037_viral_video_creators_quiz--survey_templates.xlsx
+++ b/survey_templates/037_viral_video_creators_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_"yes,_i've_been_making_videos_for_1_year_or_less"}</t>
+          <t>yes,_i've_been_making_videos_for_1_year_or_less</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': "Yes, I've been making videos for 1 year or less"}</t>
+          <t>Yes, I've been making videos for 1 year or less</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_"yes,_i've_been_making_videos_for_1-2_years"}</t>
+          <t>yes,_i've_been_making_videos_for_1-2_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': "Yes, I've been making videos for 1-2 years"}</t>
+          <t>Yes, I've been making videos for 1-2 years</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_"yes,_i've_been_making_videos_for_2-5_years"}</t>
+          <t>yes,_i've_been_making_videos_for_2-5_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': "Yes, I've been making videos for 2-5 years"}</t>
+          <t>Yes, I've been making videos for 2-5 years</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_"yes,_i've_been_making_videos_for_5_years_or_more"}</t>
+          <t>yes,_i've_been_making_videos_for_5_years_or_more</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': "Yes, I've been making videos for 5 years or more"}</t>
+          <t>Yes, I've been making videos for 5 years or more</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_"i've_done_a_little_bit_of_video_creation,_but_not_for_report"}</t>
+          <t>i've_done_a_little_bit_of_video_creation,_but_not_for_report</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': "I've done a little bit of video creation, but not for report"}</t>
+          <t>I've done a little bit of video creation, but not for report</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'vlogging'}</t>
+          <t>vlogging</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Vlogging'}</t>
+          <t>Vlogging</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'gaming'}</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Gaming'}</t>
+          <t>Gaming</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'educational'}</t>
+          <t>educational</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Educational'}</t>
+          <t>Educational</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'entertainment'}</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Entertainment'}</t>
+          <t>Entertainment</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_"i_don't_create_videos_for_a_living"}</t>
+          <t>i_don't_create_videos_for_a_living</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': "I don't create videos for a living"}</t>
+          <t>I don't create videos for a living</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'sponsorships'}</t>
+          <t>sponsorships</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Sponsorships'}</t>
+          <t>Sponsorships</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'merchandise'}</t>
+          <t>merchandise</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Merchandise'}</t>
+          <t>Merchandise</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'affiliate_marketing'}</t>
+          <t>affiliate_marketing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Affiliate marketing'}</t>
+          <t>Affiliate marketing</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'brands'}</t>
+          <t>brands</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Brands'}</t>
+          <t>Brands</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'advertisements'}</t>
+          <t>advertisements</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Advertisements'}</t>
+          <t>Advertisements</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'affiliate_marketing'}</t>
+          <t>affiliate_marketing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Affiliate marketing'}</t>
+          <t>Affiliate marketing</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'t-shirts'}</t>
+          <t>t-shirts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'T-shirts'}</t>
+          <t>T-shirts</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'hats'}</t>
+          <t>hats</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Hats'}</t>
+          <t>Hats</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'posters'}</t>
+          <t>posters</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Posters'}</t>
+          <t>Posters</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'google_adsense'}</t>
+          <t>google_adsense</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Google AdSense'}</t>
+          <t>Google AdSense</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'amazon_associates'}</t>
+          <t>amazon_associates</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Amazon Associates'}</t>
+          <t>Amazon Associates</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'tiktok'}</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'TikTok'}</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'youtube'}</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'YouTube'}</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1000'}</t>
+          <t>less_than_1000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1000'}</t>
+          <t>Less than 1000</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'1000-10k'}</t>
+          <t>1000-10k</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': '1000-10k'}</t>
+          <t>1000-10k</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'10k-50k'}</t>
+          <t>10k-50k</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': '10k-50k'}</t>
+          <t>10k-50k</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'50k-100k'}</t>
+          <t>50k-100k</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': '50k-100k'}</t>
+          <t>50k-100k</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'100k+'}</t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': '100k+'}</t>
+          <t>100k+</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_$100'}</t>
+          <t>less_than_$100</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Less than $100'}</t>
+          <t>Less than $100</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'$100-1000'}</t>
+          <t>$100-1000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': '$100-1000'}</t>
+          <t>$100-1000</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'$1000-10000'}</t>
+          <t>$1000-10000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': '$1000-10000'}</t>
+          <t>$1000-10000</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'$10000-50000'}</t>
+          <t>$10000-50000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': '$10000-50000'}</t>
+          <t>$10000-50000</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'$50000+'}</t>
+          <t>$50000+</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': '$50000+'}</t>
+          <t>$50000+</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'tiktok'}</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'TikTok'}</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'youtube'}</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'YouTube'}</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'google'}</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Google'}</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Friends'}</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'online_advertising'}</t>
+          <t>online_advertising</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Online Advertising'}</t>
+          <t>Online Advertising</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
